--- a/03_Outputs/Penderisco_Sinifana/05_Economia/economia.xlsx
+++ b/03_Outputs/Penderisco_Sinifana/05_Economia/economia.xlsx
@@ -9981,10 +9981,8 @@
       <c r="F3" s="118">
         <v>20.8101026521499</v>
       </c>
-      <c r="G3" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3" s="120">
+        <v>0.0273071434600001</v>
       </c>
       <c r="H3" s="122">
         <v>4.74158890601001</v>
@@ -10399,7 +10397,7 @@
         <v>385.524769946607</v>
       </c>
       <c r="G10" s="121">
-        <v>14.3273703195501</v>
+        <v>14.3546774630101</v>
       </c>
       <c r="H10" s="123">
         <v>116.57355735655</v>
@@ -10516,10 +10514,8 @@
       <c r="F12" s="118">
         <v>21.0540599292565</v>
       </c>
-      <c r="G12" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G12" s="120">
+        <v>0.0826620082368769</v>
       </c>
       <c r="H12" s="122">
         <v>4.68065852119919</v>
@@ -10934,7 +10930,7 @@
         <v>396.695162145036</v>
       </c>
       <c r="G19" s="121">
-        <v>14.3311219186181</v>
+        <v>14.413783926855</v>
       </c>
       <c r="H19" s="123">
         <v>119.713413495927</v>
@@ -11228,10 +11224,8 @@
       <c r="F24" s="118">
         <v>33.2884210973663</v>
       </c>
-      <c r="G24" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G24" s="120">
+        <v>0.0562276360895556</v>
       </c>
       <c r="H24" s="122">
         <v>2.91165628814392</v>
@@ -11469,7 +11463,7 @@
         <v>565.249624480466</v>
       </c>
       <c r="G28" s="121">
-        <v>3.03510799766132</v>
+        <v>3.09133563375087</v>
       </c>
       <c r="H28" s="123">
         <v>201.10821303968</v>
@@ -12178,10 +12172,8 @@
       <c r="F40" s="118">
         <v>39.487483170522</v>
       </c>
-      <c r="G40" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G40" s="120">
+        <v>0.0648858440720776</v>
       </c>
       <c r="H40" s="122">
         <v>0.575364749210628</v>
@@ -12537,7 +12529,7 @@
         <v>650.704432236721</v>
       </c>
       <c r="G46" s="121">
-        <v>11.0756643058241</v>
+        <v>11.1405501498962</v>
       </c>
       <c r="H46" s="123">
         <v>200.707902366205</v>
@@ -14312,10 +14304,8 @@
       <c r="F76" s="118">
         <v>43.7599040421363</v>
       </c>
-      <c r="G76" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G76" s="120">
+        <v>0.0483342564989261</v>
       </c>
       <c r="H76" s="122">
         <v>3.10606534666854</v>
@@ -14671,7 +14661,7 @@
         <v>611.994323314286</v>
       </c>
       <c r="G82" s="121">
-        <v>23.4917427550546</v>
+        <v>23.5400770115535</v>
       </c>
       <c r="H82" s="123">
         <v>255.728393328889</v>
